--- a/Control_Financiero_2026.xlsx
+++ b/Control_Financiero_2026.xlsx
@@ -637,12 +637,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$25:$B$36</f>
+              <f>'Dashboard'!$B$25:$B$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$G$25:$G$36</f>
+              <f>'Dashboard'!$G$25:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -734,12 +734,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$25:$B$36</f>
+              <f>'Dashboard'!$B$25:$B$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$25:$C$36</f>
+              <f>'Dashboard'!$C$25:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +758,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$25:$B$36</f>
+              <f>'Dashboard'!$B$25:$B$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$25:$D$36</f>
+              <f>'Dashboard'!$D$25:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -5872,7 +5872,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>💰  DASHBOARD — Control Financiero Jul 2026 · Jun 2027</t>
+          <t>💰  DASHBOARD — Control Financiero Jul 2026 · Jul 2027</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -6088,12 +6088,12 @@
         </is>
       </c>
       <c r="C15" s="41">
-        <f>IFERROR((6820-SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)+SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Ingreso")*'Registro Diario'!$D$5:$D$504)-MAX(0,12-MAX(1,MONTH(TODAY())-6+IF(MONTH(TODAY())&lt;7,6,0)))*375)/MAX(1,DATE(2027,6,30)-TODAY()),0)</f>
+        <f>IFERROR((6820-SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)+SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Ingreso")*'Registro Diario'!$D$5:$D$504)-MAX(0,13-MAX(1,MONTH(TODAY())-6+IF(MONTH(TODAY())&lt;7,6,0)))*375)/MAX(1,DATE(2027,7,31)-TODAY()),0)</f>
         <v/>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Lo que puedes gastar al día para llegar a junio 2027</t>
+          <t>Lo que puedes gastar al día para llegar a julio 2027</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -6130,11 +6130,11 @@
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>🎯 Saldo previsto a Jun 2027</t>
+          <t>🎯 Saldo previsto a Jul 2027</t>
         </is>
       </c>
       <c r="C17" s="41">
-        <f>IFERROR(6820-SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)+SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Ingreso")*'Registro Diario'!$D$5:$D$504)-(SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)/MAX(1,TODAY()-DATE(2026,7,1)))*MAX(0,DATE(2027,6,30)-TODAY()),0)</f>
+        <f>IFERROR(6820-SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)+SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Ingreso")*'Registro Diario'!$D$5:$D$504)-(SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*'Registro Diario'!$D$5:$D$504)/MAX(1,TODAY()-DATE(2026,7,1)))*MAX(0,DATE(2027,7,31)-TODAY()),0)</f>
         <v/>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -6645,70 +6645,88 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>375</v>
+      </c>
+      <c r="D37" s="51">
+        <f>SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Gasto")*(MONTH('Registro Diario'!$B$5:$B$504)=7)*(YEAR('Registro Diario'!$B$5:$B$504)=2027)*'Registro Diario'!$D$5:$D$504)</f>
+        <v/>
+      </c>
+      <c r="E37" s="52">
+        <f>SUMPRODUCT(('Registro Diario'!$E$5:$E$504="Ingreso")*(MONTH('Registro Diario'!$B$5:$B$504)=7)*(YEAR('Registro Diario'!$B$5:$B$504)=2027)*'Registro Diario'!$D$5:$D$504)</f>
+        <v/>
+      </c>
+      <c r="F37" s="53">
+        <f>E37-C37-D37</f>
+        <v/>
+      </c>
+      <c r="G37" s="54">
+        <f>6820+SUM($F$25:F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>📊 TOTAL</t>
         </is>
       </c>
-      <c r="C37" s="62">
-        <f>SUM(C25:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="62">
-        <f>SUM(D25:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="63">
-        <f>SUM(E25:E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="64">
-        <f>SUM(F25:F36)</f>
-        <v/>
-      </c>
-      <c r="G37" s="41">
-        <f>G36</f>
-        <v/>
-      </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="65" t="inlineStr">
+      <c r="C38" s="62">
+        <f>SUM(C25:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="62">
+        <f>SUM(D25:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="63">
+        <f>SUM(E25:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="64">
+        <f>SUM(F25:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="41">
+        <f>G37</f>
+        <v/>
+      </c>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="65" t="inlineStr">
         <is>
           <t>📊 MEDIA/MES</t>
         </is>
       </c>
-      <c r="C38" s="66">
-        <f>C37/12</f>
-        <v/>
-      </c>
-      <c r="D38" s="66">
-        <f>D37/12</f>
-        <v/>
-      </c>
-      <c r="E38" s="66">
-        <f>E37/12</f>
-        <v/>
-      </c>
-      <c r="F38" s="66">
-        <f>F37/12</f>
-        <v/>
-      </c>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
+      <c r="C39" s="66">
+        <f>C38/12</f>
+        <v/>
+      </c>
+      <c r="D39" s="66">
+        <f>D38/12</f>
+        <v/>
+      </c>
+      <c r="E39" s="66">
+        <f>E38/12</f>
+        <v/>
+      </c>
+      <c r="F39" s="66">
+        <f>F38/12</f>
+        <v/>
+      </c>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
@@ -7284,7 +7302,7 @@
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25:G36">
+  <conditionalFormatting sqref="G25:G37">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
       <formula>500</formula>
     </cfRule>
